--- a/docs/1 WEB MASTER 2350 COLONNE ABCD COMPETENCE FRANCAIS 010626.xlsx
+++ b/docs/1 WEB MASTER 2350 COLONNE ABCD COMPETENCE FRANCAIS 010626.xlsx
@@ -4698,6 +4698,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b val="0"/>
       <i val="0"/>
       <sz val="12"/>
@@ -4711,70 +4742,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="11"/>
-      <color theme="4" tint="-0.25"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FF2F5496"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
@@ -4791,61 +4758,11 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <b val="0"/>
       <i val="0"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color theme="5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="11"/>
-      <color theme="5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color theme="5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FF538135"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color theme="5"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color theme="9" tint="-0.25"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -4879,6 +4796,20 @@
       <b/>
       <i val="0"/>
       <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color rgb="FF60A500"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
       <color theme="8" tint="-0.25"/>
       <name val="Aptos Display"/>
     </font>
@@ -4886,7 +4817,98 @@
       <b/>
       <i val="0"/>
       <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color rgb="FF2F5496"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color rgb="FF538135"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color theme="9" tint="-0.25"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.25"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
       <color rgb="FF002060"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -4938,28 +4960,6 @@
       <u/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FF60A500"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -5048,145 +5048,146 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5441,7 +5442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{1D863E32-3C2F-41D3-B19A-5BA4AB04DE64}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E3C247D2-533C-4F77-97C4-8E4B38985F4A}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:G1324"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="12.57421875" customHeight="1"/>
   <cols>
